--- a/Result/profitability/3013.xlsx
+++ b/Result/profitability/3013.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>-0.18</v>
       </c>
       <c r="M2" t="n">
-        <v>0.93625</v>
+        <v>1.0125</v>
       </c>
       <c r="N2" t="n">
-        <v>17.87875</v>
+        <v>18.43625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.21</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8625</v>
+        <v>0.8550000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>17.84625</v>
+        <v>18.42875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7200000000000001</v>
+        <v>0.7912500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>17.56375</v>
+        <v>18.08375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.13</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6312500000000001</v>
+        <v>0.7400000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>17.0225</v>
+        <v>17.50875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5725000000000001</v>
+        <v>0.61625</v>
       </c>
       <c r="N6" t="n">
-        <v>16.4625</v>
+        <v>16.59875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.18</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4175</v>
+        <v>0.395</v>
       </c>
       <c r="N7" t="n">
-        <v>15.395</v>
+        <v>15.31</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2275</v>
+        <v>0.2325</v>
       </c>
       <c r="N8" t="n">
-        <v>14.4775</v>
+        <v>14.39875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3013</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3219</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2558</v>
+      </c>
+      <c r="E75" t="n">
+        <v>660</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="G75" t="n">
+        <v>430</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>13.36%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-39</v>
+      </c>
+      <c r="J75" t="n">
+        <v>391</v>
+      </c>
+      <c r="K75" t="n">
+        <v>290</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.135</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.40125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.03999999999999981</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.02919708029197077</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.629999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02978723404255312</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.8699999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.611111111111111</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.890000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2339146121467228</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
